--- a/IFX_Scripts/Test_Data_Reviewer/analysis_outputs/review_productivity_summary_1000_tests.xlsx
+++ b/IFX_Scripts/Test_Data_Reviewer/analysis_outputs/review_productivity_summary_1000_tests.xlsx
@@ -7,8 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary_1000_Tests" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curve_0_to_10pct" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nominal_Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario_Curve_0_to_10pct" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonteCarlo_0_to_10pct" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,317 +428,424 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="32" customWidth="1" min="10" max="10"/>
-    <col width="32" customWidth="1" min="11" max="11"/>
-    <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="32" customWidth="1" min="13" max="13"/>
-    <col width="32" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
-    <col width="27" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="28" customWidth="1" min="19" max="19"/>
-    <col width="25" customWidth="1" min="20" max="20"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Problematic Tests (%)</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Problematic Tests Count</t>
+          <t>Assumption</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Full Manual Review Time (h)</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Conservative Review Time (h)</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Automated Review Time (h)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Full Manual Productivity (reviews/8h day)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Conservative Productivity (reviews/8h day)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Automated Productivity (reviews/8h day)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Automation Time Saved vs Full Manual (h)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Automation Time Saved vs Conservative (h)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Automation Throughput Gain vs Full Manual (x)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Automation Throughput Gain vs Conservative (x)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Automation Productivity Improvement vs Full Manual (%)</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Automation Productivity Improvement vs Conservative (%)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Conservative Detection (%)</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Automated Detection (%)</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Conservative Issues Found</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Automated Issues Found</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Conservative Issues Missed</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Automated Issues Missed</t>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B2" t="n">
-        <v>50</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FE insertions reviewed</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>5.416666666666667</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.8013888888888889</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.476923076923077</v>
-      </c>
-      <c r="G2" t="n">
-        <v>5.333333333333333</v>
-      </c>
-      <c r="H2" t="n">
-        <v>9.98266897746967</v>
-      </c>
-      <c r="I2" t="n">
-        <v>4.615277777777778</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.6986111111111111</v>
-      </c>
-      <c r="K2" t="n">
-        <v>6.759098786828423</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.871750433275563</v>
-      </c>
-      <c r="M2" t="n">
-        <v>575.9098786828423</v>
-      </c>
-      <c r="N2" t="n">
-        <v>87.17504332755632</v>
-      </c>
-      <c r="O2" t="n">
-        <v>85.00999999999999</v>
-      </c>
-      <c r="P2" t="n">
-        <v>97.35000000000001</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>42.505</v>
-      </c>
-      <c r="R2" t="n">
-        <v>48.675</v>
-      </c>
-      <c r="S2" t="n">
-        <v>7.495000000000002</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.324999999999998</v>
+        <v>3</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>insertions/review</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Explicit input parameter. Insertion-sensitive review effort scales with this count.</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>20</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Conservative reviewer</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Local data copy and load overhead</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.266666666666667</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.5905555555555555</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1.684210526315789</v>
-      </c>
-      <c r="G3" t="n">
-        <v>6.315789473684211</v>
-      </c>
-      <c r="H3" t="n">
-        <v>13.54656632173095</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4.159444444444444</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.6761111111111111</v>
-      </c>
-      <c r="K3" t="n">
-        <v>8.043273753527753</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2.144873000940734</v>
-      </c>
-      <c r="M3" t="n">
-        <v>704.3273753527753</v>
-      </c>
-      <c r="N3" t="n">
-        <v>114.4873000940734</v>
-      </c>
-      <c r="O3" t="n">
-        <v>85.00999999999999</v>
-      </c>
-      <c r="P3" t="n">
-        <v>97.35000000000001</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>17.002</v>
-      </c>
-      <c r="R3" t="n">
-        <v>19.47</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.998000000000001</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.5299999999999994</v>
+        <v>10</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>min/review</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>User-provided fixed overhead before review.</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C4" t="n">
-        <v>4.527777777777778</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.188888888888889</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.5202777777777777</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.766871165644172</v>
-      </c>
-      <c r="G4" t="n">
-        <v>6.728971962616822</v>
-      </c>
-      <c r="H4" t="n">
-        <v>15.37640149492792</v>
-      </c>
-      <c r="I4" t="n">
-        <v>4.0075</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.6686111111111112</v>
-      </c>
-      <c r="K4" t="n">
-        <v>8.702616123865457</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2.285104111051789</v>
-      </c>
-      <c r="M4" t="n">
-        <v>770.2616123865457</v>
-      </c>
-      <c r="N4" t="n">
-        <v>128.5104111051789</v>
-      </c>
-      <c r="O4" t="n">
-        <v>85.00999999999999</v>
-      </c>
-      <c r="P4" t="n">
-        <v>97.35000000000001</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>8.500999999999999</v>
-      </c>
-      <c r="R4" t="n">
-        <v>9.734999999999999</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.499</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.2649999999999997</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Conservative reviewer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Key parameter tests reviewed</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>700-800-900</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>tests/review</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Best-nominal-worst sensitivity band centered on the user's in-the-range-of-800 statement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Conservative reviewer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Baseline scan time per reviewed test</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>s/test</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Nominal scan effort for each reviewed key parameter test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Conservative reviewer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Problematic test investigation time</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>30-60-120</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>s/problematic test</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>User-provided 1 to 3 min range, expressed as best-nominal-worst.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Conservative reviewer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Wrap-up and reporting overhead</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>15</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>min/review</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>User-provided fixed overhead after review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Automated review</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Local data copy overhead</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>25</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>min/review</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>User-provided fixed overhead before running the automated flow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Automated review</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Problematic test handling time</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>15-30-60</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>s/problematic test</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>20 s nominal from the user with a narrow best-worst sensitivity band for scenario and Monte Carlo analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Automated review</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Wrap-up and reporting overhead</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>15</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>min/review</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>User-provided fixed overhead after review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Monte Carlo</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Distribution form</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>triangular</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>distribution</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Uses left-mode-right sampling for uncertain timing inputs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Monte Carlo</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sample count</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>samples per problematic-test point</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Higher sample count stabilizes the uncertainty bands.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Important tests in scope</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>tests</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Total important tests considered for each scenario.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Engineer workday</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>8</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>h/day</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Used to convert total review time into reviews per 8 h day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Conservative detection rate</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Detection-rate assumption preserved from the prior model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Automated detection rate</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Detection-rate assumption preserved from the prior model.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -750,7 +859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -758,15 +867,15 @@
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="32" customWidth="1" min="10" max="10"/>
-    <col width="32" customWidth="1" min="11" max="11"/>
-    <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="32" customWidth="1" min="13" max="13"/>
-    <col width="32" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
     <col width="28" customWidth="1" min="15" max="15"/>
     <col width="25" customWidth="1" min="16" max="16"/>
     <col width="27" customWidth="1" min="17" max="17"/>
@@ -879,63 +988,2166 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5.416666666666667</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.916666666666667</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.916666666666667</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.476923076923077</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.627118644067796</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4.173913043478261</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.826086956521739</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.565217391304348</v>
+      </c>
+      <c r="M2" t="n">
+        <v>182.6086956521739</v>
+      </c>
+      <c r="N2" t="n">
+        <v>156.5217391304348</v>
+      </c>
+      <c r="O2" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="P2" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>42.505</v>
+      </c>
+      <c r="R2" t="n">
+        <v>48.675</v>
+      </c>
+      <c r="S2" t="n">
+        <v>7.495000000000002</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.324999999999998</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>20</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.416666666666667</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.684210526315789</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.341463414634147</v>
+      </c>
+      <c r="H3" t="n">
+        <v>6.857142857142857</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.583333333333333</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.071428571428571</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.928571428571428</v>
+      </c>
+      <c r="M3" t="n">
+        <v>307.1428571428571</v>
+      </c>
+      <c r="N3" t="n">
+        <v>192.8571428571428</v>
+      </c>
+      <c r="O3" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="P3" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>17.002</v>
+      </c>
+      <c r="R3" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.998000000000001</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.5299999999999994</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4.527777777777778</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.916666666666667</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.766871165644172</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.742857142857143</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8.727272727272728</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.611111111111111</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.939393939393939</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3.181818181818182</v>
+      </c>
+      <c r="M4" t="n">
+        <v>393.9393939393939</v>
+      </c>
+      <c r="N4" t="n">
+        <v>218.1818181818182</v>
+      </c>
+      <c r="O4" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="P4" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>8.500999999999999</v>
+      </c>
+      <c r="R4" t="n">
+        <v>9.734999999999999</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.499</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.2649999999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="37" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="27" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Problematic Tests (%)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Problematic Tests Count</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Conservative Reviewed Tests</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Conservative Problematic Time (s/test)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Automated Problematic Time (s/test)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Conservative Review Time (h)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Automated Review Time (h)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Automation Productivity Improvement vs Conservative (%)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Conservative Detection (%)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Automated Detection (%)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Conservative Issues Found</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Automated Issues Found</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Conservative Issues Missed</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Automated Issues Missed</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Best</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>700</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.166666666666667</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I2" t="n">
+        <v>225</v>
+      </c>
+      <c r="J2" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K2" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>800</v>
+      </c>
+      <c r="E3" t="n">
+        <v>60</v>
+      </c>
+      <c r="F3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.416666666666667</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I3" t="n">
+        <v>262.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K3" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Worst</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>900</v>
+      </c>
+      <c r="E4" t="n">
+        <v>120</v>
+      </c>
+      <c r="F4" t="n">
+        <v>60</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I4" t="n">
+        <v>300</v>
+      </c>
+      <c r="J4" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K4" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Best</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>700</v>
+      </c>
+      <c r="E5" t="n">
+        <v>30</v>
+      </c>
+      <c r="F5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.416666666666667</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="I5" t="n">
+        <v>205.2631578947368</v>
+      </c>
+      <c r="J5" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K5" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8.500999999999999</v>
+      </c>
+      <c r="M5" t="n">
+        <v>9.734999999999999</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.499</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.2649999999999997</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>800</v>
+      </c>
+      <c r="E6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.916666666666667</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="I6" t="n">
+        <v>218.1818181818182</v>
+      </c>
+      <c r="J6" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K6" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L6" t="n">
+        <v>8.500999999999999</v>
+      </c>
+      <c r="M6" t="n">
+        <v>9.734999999999999</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.499</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.2649999999999997</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Worst</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>900</v>
+      </c>
+      <c r="E7" t="n">
+        <v>120</v>
+      </c>
+      <c r="F7" t="n">
+        <v>60</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="I7" t="n">
+        <v>214.2857142857142</v>
+      </c>
+      <c r="J7" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K7" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L7" t="n">
+        <v>8.500999999999999</v>
+      </c>
+      <c r="M7" t="n">
+        <v>9.734999999999999</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.499</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.2649999999999997</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" t="n">
+        <v>20</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Best</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>700</v>
+      </c>
+      <c r="E8" t="n">
+        <v>30</v>
+      </c>
+      <c r="F8" t="n">
+        <v>15</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="I8" t="n">
+        <v>190.9090909090909</v>
+      </c>
+      <c r="J8" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K8" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L8" t="n">
+        <v>17.002</v>
+      </c>
+      <c r="M8" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.998000000000001</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.5299999999999994</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>800</v>
+      </c>
+      <c r="E9" t="n">
+        <v>60</v>
+      </c>
+      <c r="F9" t="n">
+        <v>30</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.416666666666667</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="I9" t="n">
+        <v>192.8571428571428</v>
+      </c>
+      <c r="J9" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K9" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L9" t="n">
+        <v>17.002</v>
+      </c>
+      <c r="M9" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.998000000000001</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.5299999999999994</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Worst</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>900</v>
+      </c>
+      <c r="E10" t="n">
+        <v>120</v>
+      </c>
+      <c r="F10" t="n">
+        <v>60</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="I10" t="n">
+        <v>180</v>
+      </c>
+      <c r="J10" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K10" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L10" t="n">
+        <v>17.002</v>
+      </c>
+      <c r="M10" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.998000000000001</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.5299999999999994</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" t="n">
+        <v>30</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Best</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>700</v>
+      </c>
+      <c r="E11" t="n">
+        <v>30</v>
+      </c>
+      <c r="F11" t="n">
+        <v>15</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.916666666666667</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="I11" t="n">
+        <v>180</v>
+      </c>
+      <c r="J11" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K11" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L11" t="n">
+        <v>25.503</v>
+      </c>
+      <c r="M11" t="n">
+        <v>29.205</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.497000000000001</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.794999999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" t="n">
+        <v>30</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>800</v>
+      </c>
+      <c r="E12" t="n">
+        <v>60</v>
+      </c>
+      <c r="F12" t="n">
+        <v>30</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.916666666666667</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.416666666666667</v>
+      </c>
+      <c r="I12" t="n">
+        <v>176.4705882352941</v>
+      </c>
+      <c r="J12" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K12" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L12" t="n">
+        <v>25.503</v>
+      </c>
+      <c r="M12" t="n">
+        <v>29.205</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.497000000000001</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.794999999999999</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>30</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Worst</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>900</v>
+      </c>
+      <c r="E13" t="n">
+        <v>120</v>
+      </c>
+      <c r="F13" t="n">
+        <v>60</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.166666666666667</v>
+      </c>
+      <c r="I13" t="n">
+        <v>161.5384615384616</v>
+      </c>
+      <c r="J13" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K13" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L13" t="n">
+        <v>25.503</v>
+      </c>
+      <c r="M13" t="n">
+        <v>29.205</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.497000000000001</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.794999999999999</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" t="n">
+        <v>40</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Best</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>700</v>
+      </c>
+      <c r="E14" t="n">
+        <v>30</v>
+      </c>
+      <c r="F14" t="n">
+        <v>15</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="I14" t="n">
+        <v>171.4285714285714</v>
+      </c>
+      <c r="J14" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K14" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L14" t="n">
+        <v>34.004</v>
+      </c>
+      <c r="M14" t="n">
+        <v>38.94</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5.996000000000001</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.059999999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" t="n">
+        <v>40</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>800</v>
+      </c>
+      <c r="E15" t="n">
+        <v>60</v>
+      </c>
+      <c r="F15" t="n">
+        <v>30</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4.416666666666667</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="I15" t="n">
+        <v>165</v>
+      </c>
+      <c r="J15" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K15" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L15" t="n">
+        <v>34.004</v>
+      </c>
+      <c r="M15" t="n">
+        <v>38.94</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5.996000000000001</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.059999999999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" t="n">
+        <v>40</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Worst</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>900</v>
+      </c>
+      <c r="E16" t="n">
+        <v>120</v>
+      </c>
+      <c r="F16" t="n">
+        <v>60</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="I16" t="n">
+        <v>150.0000000000001</v>
+      </c>
+      <c r="J16" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K16" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L16" t="n">
+        <v>34.004</v>
+      </c>
+      <c r="M16" t="n">
+        <v>38.94</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5.996000000000001</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.059999999999999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" t="n">
+        <v>50</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Best</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>700</v>
+      </c>
+      <c r="E17" t="n">
+        <v>30</v>
+      </c>
+      <c r="F17" t="n">
+        <v>15</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.416666666666667</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.291666666666667</v>
+      </c>
+      <c r="I17" t="n">
+        <v>164.516129032258</v>
+      </c>
+      <c r="J17" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K17" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L17" t="n">
+        <v>42.505</v>
+      </c>
+      <c r="M17" t="n">
+        <v>48.675</v>
+      </c>
+      <c r="N17" t="n">
+        <v>7.495000000000002</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.324999999999998</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>50</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>800</v>
+      </c>
+      <c r="E18" t="n">
+        <v>60</v>
+      </c>
+      <c r="F18" t="n">
+        <v>30</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4.916666666666667</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.916666666666667</v>
+      </c>
+      <c r="I18" t="n">
+        <v>156.5217391304348</v>
+      </c>
+      <c r="J18" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K18" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L18" t="n">
+        <v>42.505</v>
+      </c>
+      <c r="M18" t="n">
+        <v>48.675</v>
+      </c>
+      <c r="N18" t="n">
+        <v>7.495000000000002</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.324999999999998</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" t="n">
+        <v>50</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Worst</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>900</v>
+      </c>
+      <c r="E19" t="n">
+        <v>120</v>
+      </c>
+      <c r="F19" t="n">
+        <v>60</v>
+      </c>
+      <c r="G19" t="n">
+        <v>7.666666666666667</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="I19" t="n">
+        <v>142.1052631578948</v>
+      </c>
+      <c r="J19" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K19" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L19" t="n">
+        <v>42.505</v>
+      </c>
+      <c r="M19" t="n">
+        <v>48.675</v>
+      </c>
+      <c r="N19" t="n">
+        <v>7.495000000000002</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.324999999999998</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B20" t="n">
+        <v>60</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Best</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>700</v>
+      </c>
+      <c r="E20" t="n">
+        <v>30</v>
+      </c>
+      <c r="F20" t="n">
+        <v>15</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.416666666666667</v>
+      </c>
+      <c r="I20" t="n">
+        <v>158.8235294117647</v>
+      </c>
+      <c r="J20" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K20" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L20" t="n">
+        <v>51.006</v>
+      </c>
+      <c r="M20" t="n">
+        <v>58.41</v>
+      </c>
+      <c r="N20" t="n">
+        <v>8.994000000000002</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.589999999999998</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" t="n">
+        <v>60</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>800</v>
+      </c>
+      <c r="E21" t="n">
+        <v>60</v>
+      </c>
+      <c r="F21" t="n">
+        <v>30</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5.416666666666667</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.166666666666667</v>
+      </c>
+      <c r="I21" t="n">
+        <v>150.0000000000001</v>
+      </c>
+      <c r="J21" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K21" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L21" t="n">
+        <v>51.006</v>
+      </c>
+      <c r="M21" t="n">
+        <v>58.41</v>
+      </c>
+      <c r="N21" t="n">
+        <v>8.994000000000002</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.589999999999998</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B22" t="n">
+        <v>60</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Worst</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>900</v>
+      </c>
+      <c r="E22" t="n">
+        <v>120</v>
+      </c>
+      <c r="F22" t="n">
+        <v>60</v>
+      </c>
+      <c r="G22" t="n">
+        <v>8.666666666666666</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="I22" t="n">
+        <v>136.3636363636364</v>
+      </c>
+      <c r="J22" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K22" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L22" t="n">
+        <v>51.006</v>
+      </c>
+      <c r="M22" t="n">
+        <v>58.41</v>
+      </c>
+      <c r="N22" t="n">
+        <v>8.994000000000002</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.589999999999998</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>7</v>
+      </c>
+      <c r="B23" t="n">
+        <v>70</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Best</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>700</v>
+      </c>
+      <c r="E23" t="n">
+        <v>30</v>
+      </c>
+      <c r="F23" t="n">
+        <v>15</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.916666666666667</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.541666666666667</v>
+      </c>
+      <c r="I23" t="n">
+        <v>154.054054054054</v>
+      </c>
+      <c r="J23" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K23" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L23" t="n">
+        <v>59.507</v>
+      </c>
+      <c r="M23" t="n">
+        <v>68.145</v>
+      </c>
+      <c r="N23" t="n">
+        <v>10.493</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.854999999999998</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" t="n">
+        <v>70</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>800</v>
+      </c>
+      <c r="E24" t="n">
+        <v>60</v>
+      </c>
+      <c r="F24" t="n">
+        <v>30</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5.916666666666667</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.416666666666667</v>
+      </c>
+      <c r="I24" t="n">
+        <v>144.8275862068966</v>
+      </c>
+      <c r="J24" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K24" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L24" t="n">
+        <v>59.507</v>
+      </c>
+      <c r="M24" t="n">
+        <v>68.145</v>
+      </c>
+      <c r="N24" t="n">
+        <v>10.493</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.854999999999998</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" t="n">
+        <v>70</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Worst</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>900</v>
+      </c>
+      <c r="E25" t="n">
+        <v>120</v>
+      </c>
+      <c r="F25" t="n">
+        <v>60</v>
+      </c>
+      <c r="G25" t="n">
+        <v>9.666666666666666</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.166666666666667</v>
+      </c>
+      <c r="I25" t="n">
+        <v>132</v>
+      </c>
+      <c r="J25" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K25" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L25" t="n">
+        <v>59.507</v>
+      </c>
+      <c r="M25" t="n">
+        <v>68.145</v>
+      </c>
+      <c r="N25" t="n">
+        <v>10.493</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.854999999999998</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>8</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Best</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>700</v>
+      </c>
+      <c r="E26" t="n">
+        <v>30</v>
+      </c>
+      <c r="F26" t="n">
+        <v>15</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4.166666666666667</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="I26" t="n">
+        <v>150</v>
+      </c>
+      <c r="J26" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K26" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L26" t="n">
+        <v>68.008</v>
+      </c>
+      <c r="M26" t="n">
+        <v>77.88</v>
+      </c>
+      <c r="N26" t="n">
+        <v>11.992</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.119999999999997</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>800</v>
+      </c>
+      <c r="E27" t="n">
+        <v>60</v>
+      </c>
+      <c r="F27" t="n">
+        <v>30</v>
+      </c>
+      <c r="G27" t="n">
+        <v>6.416666666666667</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="I27" t="n">
+        <v>140.6250000000001</v>
+      </c>
+      <c r="J27" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K27" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L27" t="n">
+        <v>68.008</v>
+      </c>
+      <c r="M27" t="n">
+        <v>77.88</v>
+      </c>
+      <c r="N27" t="n">
+        <v>11.992</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.119999999999997</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Worst</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>900</v>
+      </c>
+      <c r="E28" t="n">
+        <v>120</v>
+      </c>
+      <c r="F28" t="n">
+        <v>60</v>
+      </c>
+      <c r="G28" t="n">
+        <v>10.66666666666667</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="I28" t="n">
+        <v>128.5714285714286</v>
+      </c>
+      <c r="J28" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K28" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L28" t="n">
+        <v>68.008</v>
+      </c>
+      <c r="M28" t="n">
+        <v>77.88</v>
+      </c>
+      <c r="N28" t="n">
+        <v>11.992</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.119999999999997</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>9</v>
+      </c>
+      <c r="B29" t="n">
+        <v>90</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Best</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>700</v>
+      </c>
+      <c r="E29" t="n">
+        <v>30</v>
+      </c>
+      <c r="F29" t="n">
+        <v>15</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4.416666666666667</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.791666666666667</v>
+      </c>
+      <c r="I29" t="n">
+        <v>146.5116279069767</v>
+      </c>
+      <c r="J29" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K29" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L29" t="n">
+        <v>76.509</v>
+      </c>
+      <c r="M29" t="n">
+        <v>87.61500000000001</v>
+      </c>
+      <c r="N29" t="n">
+        <v>13.491</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.384999999999997</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>9</v>
+      </c>
+      <c r="B30" t="n">
+        <v>90</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>800</v>
+      </c>
+      <c r="E30" t="n">
+        <v>60</v>
+      </c>
+      <c r="F30" t="n">
+        <v>30</v>
+      </c>
+      <c r="G30" t="n">
+        <v>6.916666666666667</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.916666666666667</v>
+      </c>
+      <c r="I30" t="n">
+        <v>137.1428571428571</v>
+      </c>
+      <c r="J30" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K30" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L30" t="n">
+        <v>76.509</v>
+      </c>
+      <c r="M30" t="n">
+        <v>87.61500000000001</v>
+      </c>
+      <c r="N30" t="n">
+        <v>13.491</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.384999999999997</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>9</v>
+      </c>
+      <c r="B31" t="n">
+        <v>90</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Worst</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>900</v>
+      </c>
+      <c r="E31" t="n">
+        <v>120</v>
+      </c>
+      <c r="F31" t="n">
+        <v>60</v>
+      </c>
+      <c r="G31" t="n">
+        <v>11.66666666666667</v>
+      </c>
+      <c r="H31" t="n">
+        <v>5.166666666666667</v>
+      </c>
+      <c r="I31" t="n">
+        <v>125.8064516129032</v>
+      </c>
+      <c r="J31" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K31" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L31" t="n">
+        <v>76.509</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87.61500000000001</v>
+      </c>
+      <c r="N31" t="n">
+        <v>13.491</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.384999999999997</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B32" t="n">
+        <v>100</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Best</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>700</v>
+      </c>
+      <c r="E32" t="n">
+        <v>30</v>
+      </c>
+      <c r="F32" t="n">
+        <v>15</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.916666666666667</v>
+      </c>
+      <c r="I32" t="n">
+        <v>143.4782608695652</v>
+      </c>
+      <c r="J32" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K32" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L32" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="M32" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="N32" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.649999999999997</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>10</v>
+      </c>
+      <c r="B33" t="n">
+        <v>100</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>800</v>
+      </c>
+      <c r="E33" t="n">
+        <v>60</v>
+      </c>
+      <c r="F33" t="n">
+        <v>30</v>
+      </c>
+      <c r="G33" t="n">
+        <v>7.416666666666667</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="I33" t="n">
+        <v>134.2105263157895</v>
+      </c>
+      <c r="J33" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K33" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L33" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="M33" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="N33" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.649999999999997</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>10</v>
+      </c>
+      <c r="B34" t="n">
+        <v>100</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Worst</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>900</v>
+      </c>
+      <c r="E34" t="n">
+        <v>120</v>
+      </c>
+      <c r="F34" t="n">
+        <v>60</v>
+      </c>
+      <c r="G34" t="n">
+        <v>12.66666666666667</v>
+      </c>
+      <c r="H34" t="n">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="I34" t="n">
+        <v>123.5294117647058</v>
+      </c>
+      <c r="J34" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="K34" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="L34" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="M34" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="N34" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.649999999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="31" customWidth="1" min="11" max="11"/>
+    <col width="31" customWidth="1" min="12" max="12"/>
+    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="31" customWidth="1" min="14" max="14"/>
+    <col width="35" customWidth="1" min="15" max="15"/>
+    <col width="33" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="17" max="17"/>
+    <col width="34" customWidth="1" min="18" max="18"/>
+    <col width="34" customWidth="1" min="19" max="19"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="28" customWidth="1" min="21" max="21"/>
+    <col width="25" customWidth="1" min="22" max="22"/>
+    <col width="27" customWidth="1" min="23" max="23"/>
+    <col width="24" customWidth="1" min="24" max="24"/>
+    <col width="28" customWidth="1" min="25" max="25"/>
+    <col width="25" customWidth="1" min="26" max="26"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Problematic Tests (%)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Problematic Tests Count</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Conservative Review Time Mean (h)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Conservative Review Time P5 (h)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Conservative Review Time P10 (h)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Conservative Review Time P50 (h)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Conservative Review Time P90 (h)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Conservative Review Time P95 (h)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Automated Review Time Mean (h)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Automated Review Time P5 (h)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Automated Review Time P10 (h)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Automated Review Time P50 (h)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Automated Review Time P90 (h)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Automated Review Time P95 (h)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Productivity Improvement Mean (%)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Productivity Improvement P5 (%)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Productivity Improvement P10 (%)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Productivity Improvement P50 (%)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Productivity Improvement P90 (%)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Productivity Improvement P95 (%)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Conservative Detection (%)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Automated Detection (%)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Conservative Issues Found</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Automated Issues Found</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Conservative Issues Missed</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Automated Issues Missed</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
       <c r="C2" t="n">
-        <v>4.305555555555555</v>
+        <v>2.41542926410076</v>
       </c>
       <c r="D2" t="n">
-        <v>1.111111111111111</v>
+        <v>2.246478682392416</v>
       </c>
       <c r="E2" t="n">
-        <v>0.45</v>
+        <v>2.27925600312458</v>
       </c>
       <c r="F2" t="n">
-        <v>1.858064516129032</v>
+        <v>2.414654288271523</v>
       </c>
       <c r="G2" t="n">
-        <v>7.199999999999999</v>
+        <v>2.553410394749022</v>
       </c>
       <c r="H2" t="n">
-        <v>17.77777777777778</v>
+        <v>2.58671255349482</v>
       </c>
       <c r="I2" t="n">
-        <v>3.855555555555555</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6611111111111112</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="K2" t="n">
-        <v>9.5679012345679</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L2" t="n">
-        <v>2.469135802469136</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="M2" t="n">
-        <v>856.7901234567901</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N2" t="n">
-        <v>146.9135802469136</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="O2" t="n">
-        <v>85.00999999999999</v>
+        <v>262.3143896151141</v>
       </c>
       <c r="P2" t="n">
-        <v>97.35000000000001</v>
+        <v>236.9718023588624</v>
       </c>
       <c r="Q2" t="n">
+        <v>241.8884004686871</v>
+      </c>
+      <c r="R2" t="n">
+        <v>262.1981432407284</v>
+      </c>
+      <c r="S2" t="n">
+        <v>283.0115592123534</v>
+      </c>
+      <c r="T2" t="n">
+        <v>288.0068830242229</v>
+      </c>
+      <c r="U2" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="V2" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="W2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="n">
+      <c r="X2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="n">
+      <c r="Y2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="n">
+      <c r="Z2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -947,57 +3159,75 @@
         <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>4.527777777777778</v>
+        <v>3.001110623380278</v>
       </c>
       <c r="D3" t="n">
-        <v>1.188888888888889</v>
+        <v>2.706351069685059</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5202777777777777</v>
+        <v>2.764047877201064</v>
       </c>
       <c r="F3" t="n">
-        <v>1.766871165644172</v>
+        <v>2.993760130837439</v>
       </c>
       <c r="G3" t="n">
-        <v>6.728971962616822</v>
+        <v>3.251304885881086</v>
       </c>
       <c r="H3" t="n">
-        <v>15.37640149492792</v>
+        <v>3.325149131091008</v>
       </c>
       <c r="I3" t="n">
-        <v>4.0075</v>
+        <v>0.9594683195497042</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6686111111111112</v>
+        <v>0.839625504495207</v>
       </c>
       <c r="K3" t="n">
-        <v>8.702616123865457</v>
+        <v>0.8624905864262778</v>
       </c>
       <c r="L3" t="n">
-        <v>2.285104111051789</v>
+        <v>0.9507735928704663</v>
       </c>
       <c r="M3" t="n">
-        <v>770.2616123865457</v>
+        <v>1.068882563275277</v>
       </c>
       <c r="N3" t="n">
-        <v>128.5104111051789</v>
+        <v>1.098509573925227</v>
       </c>
       <c r="O3" t="n">
-        <v>85.00999999999999</v>
+        <v>214.8893624112742</v>
       </c>
       <c r="P3" t="n">
-        <v>97.35000000000001</v>
+        <v>163.7188421331592</v>
       </c>
       <c r="Q3" t="n">
+        <v>172.9542307270803</v>
+      </c>
+      <c r="R3" t="n">
+        <v>213.1777947488845</v>
+      </c>
+      <c r="S3" t="n">
+        <v>259.0501332453181</v>
+      </c>
+      <c r="T3" t="n">
+        <v>270.9749024703061</v>
+      </c>
+      <c r="U3" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="V3" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="W3" t="n">
         <v>8.500999999999999</v>
       </c>
-      <c r="R3" t="n">
+      <c r="X3" t="n">
         <v>9.734999999999999</v>
       </c>
-      <c r="S3" t="n">
+      <c r="Y3" t="n">
         <v>1.499</v>
       </c>
-      <c r="T3" t="n">
+      <c r="Z3" t="n">
         <v>0.2649999999999997</v>
       </c>
     </row>
@@ -1009,57 +3239,75 @@
         <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>4.75</v>
+        <v>3.590088637652948</v>
       </c>
       <c r="D4" t="n">
-        <v>1.266666666666667</v>
+        <v>3.082847601887768</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5905555555555555</v>
+        <v>3.177715608350608</v>
       </c>
       <c r="F4" t="n">
-        <v>1.684210526315789</v>
+        <v>3.565346485819578</v>
       </c>
       <c r="G4" t="n">
-        <v>6.315789473684211</v>
+        <v>4.054617985033545</v>
       </c>
       <c r="H4" t="n">
-        <v>13.54656632173095</v>
+        <v>4.182326680062856</v>
       </c>
       <c r="I4" t="n">
-        <v>4.159444444444444</v>
+        <v>1.250124373352762</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6761111111111111</v>
+        <v>1.015726638536423</v>
       </c>
       <c r="K4" t="n">
-        <v>8.043273753527753</v>
+        <v>1.051360083952513</v>
       </c>
       <c r="L4" t="n">
-        <v>2.144873000940734</v>
+        <v>1.235050019811935</v>
       </c>
       <c r="M4" t="n">
-        <v>704.3273753527753</v>
+        <v>1.474678474253303</v>
       </c>
       <c r="N4" t="n">
-        <v>114.4873000940734</v>
+        <v>1.527465374781552</v>
       </c>
       <c r="O4" t="n">
-        <v>85.00999999999999</v>
+        <v>191.7007932213192</v>
       </c>
       <c r="P4" t="n">
-        <v>97.35000000000001</v>
+        <v>123.3110860354427</v>
       </c>
       <c r="Q4" t="n">
+        <v>135.2125099147114</v>
+      </c>
+      <c r="R4" t="n">
+        <v>187.9953562264546</v>
+      </c>
+      <c r="S4" t="n">
+        <v>253.0882465113896</v>
+      </c>
+      <c r="T4" t="n">
+        <v>273.3114793803077</v>
+      </c>
+      <c r="U4" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="V4" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="W4" t="n">
         <v>17.002</v>
       </c>
-      <c r="R4" t="n">
+      <c r="X4" t="n">
         <v>19.47</v>
       </c>
-      <c r="S4" t="n">
+      <c r="Y4" t="n">
         <v>2.998000000000001</v>
       </c>
-      <c r="T4" t="n">
+      <c r="Z4" t="n">
         <v>0.5299999999999994</v>
       </c>
     </row>
@@ -1071,57 +3319,75 @@
         <v>30</v>
       </c>
       <c r="C5" t="n">
-        <v>4.972222222222222</v>
+        <v>4.16211934074181</v>
       </c>
       <c r="D5" t="n">
-        <v>1.344444444444445</v>
+        <v>3.428495151846787</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6608333333333334</v>
+        <v>3.572675472550186</v>
       </c>
       <c r="F5" t="n">
-        <v>1.608938547486033</v>
+        <v>4.115728784548502</v>
       </c>
       <c r="G5" t="n">
-        <v>5.950413223140496</v>
+        <v>4.838227074090382</v>
       </c>
       <c r="H5" t="n">
-        <v>12.10592686002522</v>
+        <v>5.019811444502543</v>
       </c>
       <c r="I5" t="n">
-        <v>4.311388888888889</v>
+        <v>1.54338239029007</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6836111111111112</v>
+        <v>1.181804618034854</v>
       </c>
       <c r="K5" t="n">
-        <v>7.524169819251786</v>
+        <v>1.246196745585761</v>
       </c>
       <c r="L5" t="n">
-        <v>2.034468263976461</v>
+        <v>1.518221532499442</v>
       </c>
       <c r="M5" t="n">
-        <v>652.4169819251786</v>
+        <v>1.880684202641496</v>
       </c>
       <c r="N5" t="n">
-        <v>103.4468263976461</v>
+        <v>1.969543203060409</v>
       </c>
       <c r="O5" t="n">
-        <v>85.00999999999999</v>
+        <v>176.0246037869624</v>
       </c>
       <c r="P5" t="n">
-        <v>97.35000000000001</v>
+        <v>97.04060711539081</v>
       </c>
       <c r="Q5" t="n">
+        <v>110.5544381193533</v>
+      </c>
+      <c r="R5" t="n">
+        <v>170.5326450610138</v>
+      </c>
+      <c r="S5" t="n">
+        <v>249.3447730819312</v>
+      </c>
+      <c r="T5" t="n">
+        <v>270.5946712007901</v>
+      </c>
+      <c r="U5" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="V5" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="W5" t="n">
         <v>25.503</v>
       </c>
-      <c r="R5" t="n">
+      <c r="X5" t="n">
         <v>29.205</v>
       </c>
-      <c r="S5" t="n">
+      <c r="Y5" t="n">
         <v>4.497000000000001</v>
       </c>
-      <c r="T5" t="n">
+      <c r="Z5" t="n">
         <v>0.794999999999999</v>
       </c>
     </row>
@@ -1133,57 +3399,75 @@
         <v>40</v>
       </c>
       <c r="C6" t="n">
-        <v>5.194444444444445</v>
+        <v>4.746758616898815</v>
       </c>
       <c r="D6" t="n">
-        <v>1.422222222222222</v>
+        <v>3.801583096778252</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7311111111111112</v>
+        <v>3.957854052234877</v>
       </c>
       <c r="F6" t="n">
-        <v>1.540106951871658</v>
+        <v>4.686180688115035</v>
       </c>
       <c r="G6" t="n">
-        <v>5.625</v>
+        <v>5.657478239544314</v>
       </c>
       <c r="H6" t="n">
-        <v>10.94224924012158</v>
+        <v>5.88350649133243</v>
       </c>
       <c r="I6" t="n">
-        <v>4.463333333333334</v>
+        <v>1.837141189949409</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6911111111111111</v>
+        <v>1.367591720273492</v>
       </c>
       <c r="K6" t="n">
-        <v>7.104863221884498</v>
+        <v>1.447799875169683</v>
       </c>
       <c r="L6" t="n">
-        <v>1.945288753799392</v>
+        <v>1.807940595425988</v>
       </c>
       <c r="M6" t="n">
-        <v>610.4863221884498</v>
+        <v>2.283395733432393</v>
       </c>
       <c r="N6" t="n">
-        <v>94.52887537993921</v>
+        <v>2.393404841492889</v>
       </c>
       <c r="O6" t="n">
-        <v>85.00999999999999</v>
+        <v>165.7032605713464</v>
       </c>
       <c r="P6" t="n">
-        <v>97.35000000000001</v>
+        <v>82.66283752578777</v>
       </c>
       <c r="Q6" t="n">
+        <v>95.70671228103866</v>
+      </c>
+      <c r="R6" t="n">
+        <v>160.1391582279179</v>
+      </c>
+      <c r="S6" t="n">
+        <v>241.5558308069191</v>
+      </c>
+      <c r="T6" t="n">
+        <v>269.0000704284981</v>
+      </c>
+      <c r="U6" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="V6" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="W6" t="n">
         <v>34.004</v>
       </c>
-      <c r="R6" t="n">
+      <c r="X6" t="n">
         <v>38.94</v>
       </c>
-      <c r="S6" t="n">
+      <c r="Y6" t="n">
         <v>5.996000000000001</v>
       </c>
-      <c r="T6" t="n">
+      <c r="Z6" t="n">
         <v>1.059999999999999</v>
       </c>
     </row>
@@ -1195,57 +3479,75 @@
         <v>50</v>
       </c>
       <c r="C7" t="n">
-        <v>5.416666666666667</v>
+        <v>5.329380138680914</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5</v>
+        <v>4.139234751163563</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8013888888888889</v>
+        <v>4.344630667623287</v>
       </c>
       <c r="F7" t="n">
-        <v>1.476923076923077</v>
+        <v>5.244683503328989</v>
       </c>
       <c r="G7" t="n">
-        <v>5.333333333333333</v>
+        <v>6.485236690338054</v>
       </c>
       <c r="H7" t="n">
-        <v>9.98266897746967</v>
+        <v>6.758945898591254</v>
       </c>
       <c r="I7" t="n">
-        <v>4.615277777777778</v>
+        <v>2.120887728435583</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6986111111111111</v>
+        <v>1.532284105475524</v>
       </c>
       <c r="K7" t="n">
-        <v>6.759098786828423</v>
+        <v>1.631163015059807</v>
       </c>
       <c r="L7" t="n">
-        <v>1.871750433275563</v>
+        <v>2.085053754016501</v>
       </c>
       <c r="M7" t="n">
-        <v>575.9098786828423</v>
+        <v>2.68312310396986</v>
       </c>
       <c r="N7" t="n">
-        <v>87.17504332755632</v>
+        <v>2.837582725544976</v>
       </c>
       <c r="O7" t="n">
-        <v>85.00999999999999</v>
+        <v>159.9790095859167</v>
       </c>
       <c r="P7" t="n">
-        <v>97.35000000000001</v>
+        <v>72.76214025704681</v>
       </c>
       <c r="Q7" t="n">
+        <v>86.75822642911298</v>
+      </c>
+      <c r="R7" t="n">
+        <v>151.8605997348663</v>
+      </c>
+      <c r="S7" t="n">
+        <v>245.6906126839537</v>
+      </c>
+      <c r="T7" t="n">
+        <v>273.7729944840139</v>
+      </c>
+      <c r="U7" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="V7" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="W7" t="n">
         <v>42.505</v>
       </c>
-      <c r="R7" t="n">
+      <c r="X7" t="n">
         <v>48.675</v>
       </c>
-      <c r="S7" t="n">
+      <c r="Y7" t="n">
         <v>7.495000000000002</v>
       </c>
-      <c r="T7" t="n">
+      <c r="Z7" t="n">
         <v>1.324999999999998</v>
       </c>
     </row>
@@ -1257,57 +3559,75 @@
         <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>5.638888888888889</v>
+        <v>5.916034859162549</v>
       </c>
       <c r="D8" t="n">
-        <v>1.577777777777778</v>
+        <v>4.469426027452005</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8716666666666667</v>
+        <v>4.729997951930824</v>
       </c>
       <c r="F8" t="n">
-        <v>1.41871921182266</v>
+        <v>5.820617330936006</v>
       </c>
       <c r="G8" t="n">
-        <v>5.070422535211268</v>
+        <v>7.261103364384983</v>
       </c>
       <c r="H8" t="n">
-        <v>9.177820267686425</v>
+        <v>7.610505017543737</v>
       </c>
       <c r="I8" t="n">
-        <v>4.767222222222222</v>
+        <v>2.434652518758236</v>
       </c>
       <c r="J8" t="n">
-        <v>0.706111111111111</v>
+        <v>1.726197023617015</v>
       </c>
       <c r="K8" t="n">
-        <v>6.469088591459529</v>
+        <v>1.850105985777661</v>
       </c>
       <c r="L8" t="n">
-        <v>1.810070108349267</v>
+        <v>2.382536397941561</v>
       </c>
       <c r="M8" t="n">
-        <v>546.9088591459529</v>
+        <v>3.116126301624199</v>
       </c>
       <c r="N8" t="n">
-        <v>81.00701083492669</v>
+        <v>3.265435247552973</v>
       </c>
       <c r="O8" t="n">
-        <v>85.00999999999999</v>
+        <v>152.209544591456</v>
       </c>
       <c r="P8" t="n">
-        <v>97.35000000000001</v>
+        <v>61.42986681125879</v>
       </c>
       <c r="Q8" t="n">
+        <v>76.31374063906539</v>
+      </c>
+      <c r="R8" t="n">
+        <v>144.752888580879</v>
+      </c>
+      <c r="S8" t="n">
+        <v>238.9543702727345</v>
+      </c>
+      <c r="T8" t="n">
+        <v>268.7571257742824</v>
+      </c>
+      <c r="U8" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="V8" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="W8" t="n">
         <v>51.006</v>
       </c>
-      <c r="R8" t="n">
+      <c r="X8" t="n">
         <v>58.41</v>
       </c>
-      <c r="S8" t="n">
+      <c r="Y8" t="n">
         <v>8.994000000000002</v>
       </c>
-      <c r="T8" t="n">
+      <c r="Z8" t="n">
         <v>1.589999999999998</v>
       </c>
     </row>
@@ -1319,57 +3639,75 @@
         <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>5.861111111111111</v>
+        <v>6.492231887491156</v>
       </c>
       <c r="D9" t="n">
-        <v>1.655555555555555</v>
+        <v>4.827644538228248</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9419444444444445</v>
+        <v>5.1160625888939</v>
       </c>
       <c r="F9" t="n">
-        <v>1.364928909952607</v>
+        <v>6.380803912382113</v>
       </c>
       <c r="G9" t="n">
-        <v>4.832214765100671</v>
+        <v>8.049721387896229</v>
       </c>
       <c r="H9" t="n">
-        <v>8.493069890887643</v>
+        <v>8.472951184251833</v>
       </c>
       <c r="I9" t="n">
-        <v>4.919166666666666</v>
+        <v>2.708276478023254</v>
       </c>
       <c r="J9" t="n">
-        <v>0.713611111111111</v>
+        <v>1.868486312615711</v>
       </c>
       <c r="K9" t="n">
-        <v>6.2223532881156</v>
+        <v>2.017995883407511</v>
       </c>
       <c r="L9" t="n">
-        <v>1.757593630197582</v>
+        <v>2.646823094192809</v>
       </c>
       <c r="M9" t="n">
-        <v>522.23532881156</v>
+        <v>3.498464571616913</v>
       </c>
       <c r="N9" t="n">
-        <v>75.75936301975817</v>
+        <v>3.672625046883039</v>
       </c>
       <c r="O9" t="n">
-        <v>85.00999999999999</v>
+        <v>149.917348934797</v>
       </c>
       <c r="P9" t="n">
-        <v>97.35000000000001</v>
+        <v>56.3461947133698</v>
       </c>
       <c r="Q9" t="n">
+        <v>72.26084285914324</v>
+      </c>
+      <c r="R9" t="n">
+        <v>140.3712443154512</v>
+      </c>
+      <c r="S9" t="n">
+        <v>241.7010462840406</v>
+      </c>
+      <c r="T9" t="n">
+        <v>274.7160187392076</v>
+      </c>
+      <c r="U9" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="V9" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="W9" t="n">
         <v>59.507</v>
       </c>
-      <c r="R9" t="n">
+      <c r="X9" t="n">
         <v>68.145</v>
       </c>
-      <c r="S9" t="n">
+      <c r="Y9" t="n">
         <v>10.493</v>
       </c>
-      <c r="T9" t="n">
+      <c r="Z9" t="n">
         <v>1.854999999999998</v>
       </c>
     </row>
@@ -1381,57 +3719,75 @@
         <v>80</v>
       </c>
       <c r="C10" t="n">
-        <v>6.083333333333333</v>
+        <v>7.071024129446186</v>
       </c>
       <c r="D10" t="n">
-        <v>1.733333333333333</v>
+        <v>5.188046147172234</v>
       </c>
       <c r="E10" t="n">
-        <v>1.012222222222222</v>
+        <v>5.53280858218421</v>
       </c>
       <c r="F10" t="n">
-        <v>1.315068493150685</v>
+        <v>6.939711364115134</v>
       </c>
       <c r="G10" t="n">
-        <v>4.615384615384615</v>
+        <v>8.860913152205704</v>
       </c>
       <c r="H10" t="n">
-        <v>7.903402854006587</v>
+        <v>9.323915197122258</v>
       </c>
       <c r="I10" t="n">
-        <v>5.071111111111111</v>
+        <v>2.990960415656558</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7211111111111113</v>
+        <v>2.05436959537781</v>
       </c>
       <c r="K10" t="n">
-        <v>6.009879253567508</v>
+        <v>2.217189905011219</v>
       </c>
       <c r="L10" t="n">
-        <v>1.712403951701427</v>
+        <v>2.921668494211386</v>
       </c>
       <c r="M10" t="n">
-        <v>500.9879253567508</v>
+        <v>3.884867989246636</v>
       </c>
       <c r="N10" t="n">
-        <v>71.2403951701427</v>
+        <v>4.086606205969977</v>
       </c>
       <c r="O10" t="n">
-        <v>85.00999999999999</v>
+        <v>146.88615291635</v>
       </c>
       <c r="P10" t="n">
-        <v>97.35000000000001</v>
+        <v>53.13543254707708</v>
       </c>
       <c r="Q10" t="n">
+        <v>66.93365638406382</v>
+      </c>
+      <c r="R10" t="n">
+        <v>137.3999839974263</v>
+      </c>
+      <c r="S10" t="n">
+        <v>241.5570984761281</v>
+      </c>
+      <c r="T10" t="n">
+        <v>274.0356412042938</v>
+      </c>
+      <c r="U10" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="V10" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="W10" t="n">
         <v>68.008</v>
       </c>
-      <c r="R10" t="n">
+      <c r="X10" t="n">
         <v>77.88</v>
       </c>
-      <c r="S10" t="n">
+      <c r="Y10" t="n">
         <v>11.992</v>
       </c>
-      <c r="T10" t="n">
+      <c r="Z10" t="n">
         <v>2.119999999999997</v>
       </c>
     </row>
@@ -1443,57 +3799,75 @@
         <v>90</v>
       </c>
       <c r="C11" t="n">
-        <v>6.305555555555555</v>
+        <v>7.654759053425496</v>
       </c>
       <c r="D11" t="n">
-        <v>1.811111111111111</v>
+        <v>5.522252958627448</v>
       </c>
       <c r="E11" t="n">
-        <v>1.0825</v>
+        <v>5.896228454059986</v>
       </c>
       <c r="F11" t="n">
-        <v>1.268722466960353</v>
+        <v>7.504902134198893</v>
       </c>
       <c r="G11" t="n">
-        <v>4.41717791411043</v>
+        <v>9.668040453540243</v>
       </c>
       <c r="H11" t="n">
-        <v>7.390300230946884</v>
+        <v>10.17061255734082</v>
       </c>
       <c r="I11" t="n">
-        <v>5.223055555555556</v>
+        <v>3.293840128577214</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7286111111111113</v>
+        <v>2.246157025728347</v>
       </c>
       <c r="K11" t="n">
-        <v>5.824993584808828</v>
+        <v>2.413326665063859</v>
       </c>
       <c r="L11" t="n">
-        <v>1.673081857839364</v>
+        <v>3.20426186204784</v>
       </c>
       <c r="M11" t="n">
-        <v>482.4993584808828</v>
+        <v>4.304038896808728</v>
       </c>
       <c r="N11" t="n">
-        <v>67.30818578393641</v>
+        <v>4.538931015684977</v>
       </c>
       <c r="O11" t="n">
-        <v>85.00999999999999</v>
+        <v>143.2685244052855</v>
       </c>
       <c r="P11" t="n">
-        <v>97.35000000000001</v>
+        <v>47.04260767984139</v>
       </c>
       <c r="Q11" t="n">
+        <v>61.03204921442239</v>
+      </c>
+      <c r="R11" t="n">
+        <v>133.2578343036471</v>
+      </c>
+      <c r="S11" t="n">
+        <v>239.2695950044499</v>
+      </c>
+      <c r="T11" t="n">
+        <v>273.3615759724978</v>
+      </c>
+      <c r="U11" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="V11" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="W11" t="n">
         <v>76.509</v>
       </c>
-      <c r="R11" t="n">
+      <c r="X11" t="n">
         <v>87.61500000000001</v>
       </c>
-      <c r="S11" t="n">
+      <c r="Y11" t="n">
         <v>13.491</v>
       </c>
-      <c r="T11" t="n">
+      <c r="Z11" t="n">
         <v>2.384999999999997</v>
       </c>
     </row>
@@ -1505,57 +3879,75 @@
         <v>100</v>
       </c>
       <c r="C12" t="n">
-        <v>6.527777777777778</v>
+        <v>8.309789495394531</v>
       </c>
       <c r="D12" t="n">
-        <v>1.888888888888889</v>
+        <v>5.858987995452119</v>
       </c>
       <c r="E12" t="n">
-        <v>1.152777777777778</v>
+        <v>6.260163262297675</v>
       </c>
       <c r="F12" t="n">
-        <v>1.225531914893617</v>
+        <v>8.188813301987343</v>
       </c>
       <c r="G12" t="n">
-        <v>4.235294117647059</v>
+        <v>10.56405882998529</v>
       </c>
       <c r="H12" t="n">
-        <v>6.939759036144579</v>
+        <v>11.11880064198151</v>
       </c>
       <c r="I12" t="n">
-        <v>5.375</v>
+        <v>3.586380324977599</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7361111111111112</v>
+        <v>2.415109238777545</v>
       </c>
       <c r="K12" t="n">
-        <v>5.662650602409639</v>
+        <v>2.601816464527637</v>
       </c>
       <c r="L12" t="n">
-        <v>1.63855421686747</v>
+        <v>3.511916091691036</v>
       </c>
       <c r="M12" t="n">
-        <v>466.2650602409639</v>
+        <v>4.701753128246756</v>
       </c>
       <c r="N12" t="n">
-        <v>63.85542168674701</v>
+        <v>4.997020251260428</v>
       </c>
       <c r="O12" t="n">
-        <v>85.00999999999999</v>
+        <v>142.8879191530764</v>
       </c>
       <c r="P12" t="n">
-        <v>97.35000000000001</v>
+        <v>45.5524409282788</v>
       </c>
       <c r="Q12" t="n">
-        <v>85.00999999999999</v>
+        <v>60.75874064391544</v>
       </c>
       <c r="R12" t="n">
-        <v>97.35000000000001</v>
+        <v>132.4347681572156</v>
       </c>
       <c r="S12" t="n">
+        <v>240.3964857375976</v>
+      </c>
+      <c r="T12" t="n">
+        <v>279.8208422650855</v>
+      </c>
+      <c r="U12" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="V12" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="W12" t="n">
+        <v>85.00999999999999</v>
+      </c>
+      <c r="X12" t="n">
+        <v>97.35000000000001</v>
+      </c>
+      <c r="Y12" t="n">
         <v>14.99</v>
       </c>
-      <c r="T12" t="n">
+      <c r="Z12" t="n">
         <v>2.649999999999997</v>
       </c>
     </row>
